--- a/output/review/local-2026-03-21/hematocrit_review.xlsx
+++ b/output/review/local-2026-03-21/hematocrit_review.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="hematocrit" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'hematocrit'!$A$12:$K$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'hematocrit'!$A$12:$L$120</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,20 +443,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K120"/>
+  <dimension ref="A1:L120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -592,59 +593,65 @@
       <c r="I12" s="1" t="n"/>
       <c r="J12" s="1" t="n"/>
       <c r="K12" s="1" t="n"/>
+      <c r="L12" s="1" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>LOINC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>SCTID</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>FSN</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Complete aggregation</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Quantitative (all numeric)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Quantitative &amp; convertible</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Qualitative (ordinal / nominal / presence)</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Semi-quantitative (test strip)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Panel / order code (no Property)</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Use case</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
@@ -653,27 +660,27 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19098-3</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>173061010000103</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Presence of erythrocyte in amniotic fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [Presence] in Amniotic fluid</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -681,14 +688,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -696,12 +703,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -710,27 +722,27 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>34446-5</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>133031010000108</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Presence of erythrocyte in body fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [Presence] in Body fluid</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -738,14 +750,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -753,12 +765,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -767,27 +784,27 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>99926-8</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>221781010000105</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Presence of erythrocyte in body fluid at point in time by automated technique (observable entity)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [Presence] in Body fluid by Automated</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -795,14 +812,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -810,12 +827,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -824,27 +846,27 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>88113-6</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>201171010000103</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Presence of erythrocyte in cerebrospinal fluid at point in time by Gram stain (observable entity)</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [Presence] in Cerebral spinal fluid by Gram stain</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -852,14 +874,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -867,12 +889,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -881,27 +908,27 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>68901-8</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>50031010000108</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Presence of erythrocyte in dialysate at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [Presence] in Dialysis fluid</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -909,14 +936,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -924,12 +951,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -938,27 +970,27 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>38285-3</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>68521010000107</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Presence of erythrocyte in duodenal fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [Presence] in Duodenal fluid</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -966,14 +998,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -981,12 +1013,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -995,27 +1032,27 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>72338-7</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>213861010000101</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Presence of erythrocyte in prostatic fluid at point in time by light microscopy (observable entity)</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [Presence] in Prostatic fluid by Light microscopy</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1023,14 +1060,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -1038,12 +1075,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1052,27 +1094,27 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>13627-5</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>249581010000102</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Presence of erythrocyte in seminal fluid at point in time by light microscopy (observable entity)</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [Presence] in Semen by Light microscopy</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1080,14 +1122,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -1095,12 +1137,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1109,27 +1156,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>72162-1</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>157921010000102</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Presence of erythrocyte in specimen at point in time by Gram stain (observable entity)</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [Presence] in Specimen by Gram stain</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1137,14 +1184,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -1152,12 +1199,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1166,27 +1218,27 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>70124-3</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>217731010000105</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Presence of erythrocyte in specimen at point in time by wet preparation (observable entity)</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [Presence] in Specimen by Wet preparation</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1194,14 +1246,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -1209,12 +1261,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1223,27 +1280,27 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>33668-5</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>161961010000107</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Presence of erythrocyte in stool at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [Presence] in Stool</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1251,14 +1308,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -1266,12 +1323,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1280,27 +1342,27 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>33051-4</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>97361010000106</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Presence of erythrocyte in urine at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [Presence] in Urine</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1308,14 +1370,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -1323,12 +1385,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1337,27 +1404,27 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>53292-9</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>76991010000106</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Presence of erythrocyte in urine at point in time by automated technique (observable entity)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [Presence] in Urine by Automated</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1365,14 +1432,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -1380,12 +1447,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1394,27 +1466,27 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>105090-5</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>484251010000102</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Presence of erythrocyte in urine sediment at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [Presence] in Urine sediment</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1422,14 +1494,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -1437,12 +1509,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1451,27 +1528,27 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>32776-7</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>126891010000108</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Presence of erythrocyte in urine sediment at point in time by light microscopy (observable entity)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [Presence] in Urine sediment by Light microscopy</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1479,14 +1556,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -1494,12 +1571,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1508,27 +1590,27 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>48051-7</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>153061010000100</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Presence of erythrocyte in vagina at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [Presence] in Vaginal fluid</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1536,14 +1618,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
@@ -1551,41 +1633,42 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>648131000005102</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Presence of erythrocytes in urine (observable entity)</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Presence of erythrocytes in urine</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1593,14 +1676,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -1608,12 +1691,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>Presence property → qualitative</t>
         </is>
@@ -1622,32 +1710,32 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>109724-5</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>720581010000103</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Measurement of erythrocyte in dialysate (observable entity)</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [Measurement] in Dialysis fluid</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -1665,12 +1753,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>Measurement property, no scale asserted (generic)</t>
         </is>
@@ -1679,32 +1772,32 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>99927-6</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>221051010000102</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Number areic of erythrocyte in body fluid at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/area] in Body fluid by Automated count</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -1722,12 +1815,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -1736,32 +1834,32 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>96711-7</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>41931010000100</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Number areic of erythrocyte in body fluid at point in time by light microscopy (observable entity)</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/area] in Body fluid by Light microscopy</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -1779,12 +1877,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -1793,32 +1896,32 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>51910-8</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>196681010000101</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Number areic of erythrocyte in bronchoalveolar lavage fluid at point in time by high power field light microscopy (observable entity)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/area] in Bronchoalveolar lavage by Microscopy high power field</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -1836,12 +1939,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -1850,32 +1958,32 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>96719-0</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>223251010000105</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Number areic of erythrocyte in prostatic fluid at point in time by light microscopy (observable entity)</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/area] in Prostatic fluid by Light microscopy</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
@@ -1893,12 +2001,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -1907,32 +2020,32 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>58767-5</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>76841010000107</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Number areic of erythrocyte in seminal fluid at point in time by high power field light microscopy (observable entity)</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/area] in Semen by Microscopy high power field</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -1950,12 +2063,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -1964,32 +2082,32 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>75237-8</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>181151010000105</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Number areic of erythrocyte in synovial fluid at point in time by high power field light microscopy (observable entity)</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/area] in Synovial fluid by Microscopy high power field</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -2007,12 +2125,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2021,32 +2144,32 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>51382-0</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>218251010000106</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Number areic of erythrocyte in synovial fluid at point in time by light microscopy (observable entity)</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/area] in Synovial fluid by Light microscopy</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -2064,12 +2187,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2078,32 +2206,32 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>104647-3</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>483181010000104</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Number areic of erythrocyte in urine at point in time by computer assisted (observable entity)</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Erythrocyte [#/area] in Urine by Computer assisted method</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -2121,12 +2249,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2135,32 +2268,32 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>105107-7</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>484381010000100</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Number areic of erythrocyte in urine sediment at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/area] in Urine sediment</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -2178,12 +2311,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2192,32 +2330,32 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>46419-8</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>228491010000109</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Number areic of erythrocyte in urine sediment at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/area] in Urine sediment by Automated count</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -2235,12 +2373,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="L41" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2249,32 +2392,32 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>13945-1</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>180501010000108</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Number areic of erythrocyte in urine sediment at point in time by high power field light microscopy (observable entity)</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/area] in Urine sediment by Microscopy high power field</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
@@ -2292,12 +2435,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2306,32 +2454,32 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>44242-6</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>177231010000109</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Number areic of erythrocyte in vagina at point in time by wet preparation (observable entity)</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/area] in Vaginal fluid by Wet preparation</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
@@ -2349,12 +2497,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="L43" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2363,32 +2516,32 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>43416-7</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>554311010000109</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Volume fraction of erythrocyte in ^Stem cell product at point in time by calculation (observable entity)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Hematocrit [Volume Fraction] of Stem cell product by calculation</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -2406,12 +2559,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2420,32 +2578,32 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>62241-5</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>602551010000109</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Volume fraction of erythrocyte in Bld^Fetus at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Hematocrit [Volume Fraction] of Blood from Fetus by Automated count</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
@@ -2463,12 +2621,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
+      <c r="L45" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2477,32 +2640,32 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>104874-3</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>483951010000107</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Volume fraction of erythrocyte in blood at point in time by calculation baseline (observable entity)</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Hematocrit [Volume Fraction] of Blood by calculation --baseline</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
@@ -2520,12 +2683,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2534,32 +2702,32 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>4545-0</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>558271010000104</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Volume fraction of erythrocyte in blood at point in time by centrifugation (observable entity)</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Hematocrit [Volume Fraction] of Blood by Centrifugation</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
@@ -2577,12 +2745,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="L47" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2591,32 +2764,32 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>48703-3</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>562671010000105</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Volume fraction of erythrocyte in blood at point in time by estimation (observable entity)</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Hematocrit [Volume Fraction] of Blood by Estimated</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -2634,12 +2807,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="L48" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2648,32 +2826,32 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>55781-9</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>594271010000102</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Volume fraction of erythrocyte in bone marrow at point in time by calculation (observable entity)</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Hematocrit [Volume Fraction] of Bone marrow by calculation</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -2691,12 +2869,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="L49" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2705,32 +2888,32 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>42908-4</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>552361010000103</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Volume fraction of erythrocyte in capillary blood at point in time by calculation (observable entity)</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Hematocrit [Volume Fraction] of Capillary blood by calculation</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -2748,12 +2931,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="L50" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2762,32 +2950,32 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>30398-2</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>525191010000100</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Volume fraction of erythrocyte in cerebrospinal fluid at point in time by calculation (observable entity)</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Hematocrit [Volume Fraction] of Cerebral spinal fluid by calculation</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
@@ -2805,12 +2993,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr">
+      <c r="L51" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2819,32 +3012,32 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>13508-7</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>492301010000101</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Volume fraction of erythrocyte in cerebrospinal fluid at point in time by centrifugation (observable entity)</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Hematocrit [Volume Fraction] of Cerebral spinal fluid by Centrifugation</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -2862,12 +3055,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="L52" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2876,32 +3074,32 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>11271-4</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>489951010000109</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Volume fraction of erythrocyte in cord blood at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Hematocrit [Volume Fraction] of Cord blood by Automated count</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
@@ -2919,12 +3117,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr">
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr">
+      <c r="L53" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2933,32 +3136,32 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>11151-8</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>489801010000101</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Volume fraction of erythrocyte in cord blood at point in time by calculation (observable entity)</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Hematocrit [Volume Fraction] of Cord blood by calculation</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -2976,12 +3179,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="L54" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2990,32 +3198,32 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>47640-8</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>560711010000108</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Volume fraction of erythrocyte in dialysate at point in time by calculation (observable entity)</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Hematocrit [Volume Fraction] of Dialysis fluid by calculation</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
@@ -3033,12 +3241,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
+      <c r="L55" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -3047,32 +3260,32 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>41655-2</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>539811010000101</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Volume fraction of erythrocyte in mixed venous blood at point in time by calculation (observable entity)</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Hematocrit [Volume Fraction] of Mixed venous blood by calculation</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -3090,12 +3303,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="L56" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -3104,32 +3322,32 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>107175-2</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>487771010000105</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Volume fraction of erythrocyte in peritoneal fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Hematocrit [Volume Fraction] of Peritoneal fluid</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -3147,12 +3365,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr">
+      <c r="L57" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -3161,32 +3384,32 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>70169-8</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>607531010000101</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Volume fraction of erythrocyte in pleural fluid at point in time by calculation (observable entity)</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Hematocrit [Volume Fraction] of Pleural fluid by calculation</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -3204,12 +3427,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr">
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr">
+      <c r="L58" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -3218,32 +3446,32 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>70168-0</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>607521010000104</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Volume fraction of erythrocyte in synovial fluid at point in time by calculation (observable entity)</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Hematocrit [Volume Fraction] of Synovial fluid by calculation</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -3261,12 +3489,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr">
+      <c r="L59" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -3275,32 +3508,32 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>17809-5</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>500871010000107</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Volume fraction of erythrocyte in urine at point in time by calculation (observable entity)</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Hematocrit [Volume Fraction] of Urine by calculation</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -3318,12 +3551,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="L60" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -3332,32 +3570,32 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>32354-3</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>527701010000101</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>Volume fraction of erythrocyte to arterial blood in arterial blood at point in time by calculation (observable entity)</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Hematocrit [Volume Fraction] of Arterial blood by calculation</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -3375,12 +3613,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr">
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr">
+      <c r="L61" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -3389,32 +3632,32 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>4544-3</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>558261010000109</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Volume fraction of erythrocyte to blood in blood at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Hematocrit [Volume Fraction] of Blood by Automated count</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -3432,12 +3675,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="L62" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -3446,32 +3694,32 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>20570-8</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>504981010000105</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Volume fraction of erythrocyte to blood in blood at point in time by calculation (observable entity)</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Hematocrit [Volume Fraction] of Blood by calculation</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -3489,12 +3737,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr">
+      <c r="L63" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -3503,32 +3756,32 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>31100-1</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>526231010000104</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Volume fraction of erythrocyte to blood in blood at point in time by electrical impedance (observable entity)</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Hematocrit [Volume Fraction] of Blood by Impedance</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
@@ -3546,12 +3799,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="L64" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -3560,32 +3818,32 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11153-4</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>489821010000109</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Volume fraction of erythrocyte to body fluid in body fluid at point in time by calculation (observable entity)</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Hematocrit [Volume Fraction] of Body fluid by calculation</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -3603,12 +3861,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr">
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K65" s="2" t="inlineStr">
+      <c r="L65" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -3617,32 +3880,32 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>41654-5</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>539801010000104</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Volume fraction of erythrocyte to venous blood in venous blood at point in time by calculation (observable entity)</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Hematocrit [Volume Fraction] of Venous blood by calculation</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -3660,12 +3923,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="L66" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -3674,24 +3942,24 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>30390-9</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>525161010000106</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Arbitrary concentration of erythrocyte in stool at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [Units/volume] in Stool</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3702,9 +3970,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -3717,12 +3985,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K67" s="2" t="inlineStr">
+      <c r="L67" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3731,24 +4004,24 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>14331-3</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>495631010000106</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Arbitrary concentration of erythrocyte in stool at point in time by manual count (observable entity)</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [Units/volume] in Stool by Manual count</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3759,9 +4032,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -3774,12 +4047,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr">
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
+      <c r="L68" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3788,24 +4066,24 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>55779-3</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>96551010000101</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in amniotic fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Amniotic fluid</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3816,9 +4094,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -3831,12 +4109,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr">
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K69" s="2" t="inlineStr">
+      <c r="L69" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3845,24 +4128,24 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>62240-7</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>93071010000109</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in Bld^Fetus at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Blood from Fetus by Automated count</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3873,9 +4156,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G70" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -3888,12 +4171,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr">
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr">
+      <c r="L70" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3902,24 +4190,24 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>26453-1</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>262301010000104</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Blood</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3930,9 +4218,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G71" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -3945,12 +4233,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J71" s="2" t="inlineStr">
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K71" s="2" t="inlineStr">
+      <c r="L71" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3959,24 +4252,24 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>789-8</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>249121010000107</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in blood at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Blood by Automated count</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3987,9 +4280,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -4002,12 +4295,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr">
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K72" s="2" t="inlineStr">
+      <c r="L72" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4016,24 +4314,24 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>790-6</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>176511010000101</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in blood at point in time by manual count (observable entity)</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Blood by Manual count</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4044,9 +4342,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G73" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -4059,12 +4357,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J73" s="2" t="inlineStr">
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K73" s="2" t="inlineStr">
+      <c r="L73" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4073,24 +4376,24 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>26455-6</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>182041010000104</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in body fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Body fluid</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4101,9 +4404,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -4116,12 +4419,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr">
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
+      <c r="L74" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4130,24 +4438,24 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>23860-0</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>119161010000105</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in body fluid at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Body fluid by Automated count</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4158,9 +4466,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -4173,12 +4481,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr">
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K75" s="2" t="inlineStr">
+      <c r="L75" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4187,24 +4500,24 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>6741-3</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>183111010000108</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in body fluid at point in time by manual count (observable entity)</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Body fluid by Manual count</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4215,9 +4528,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -4230,12 +4543,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr">
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K76" s="2" t="inlineStr">
+      <c r="L76" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4244,24 +4562,24 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>82588-5</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>227101010000109</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in bone marrow at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Bone marrow by Automated count</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4272,9 +4590,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -4287,12 +4605,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr">
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K77" s="2" t="inlineStr">
+      <c r="L77" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4301,24 +4624,24 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>99777-5</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>266051010000101</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in bronchoalveolar lavage fluid at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Bronchoalveolar lavage by Automated count</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4329,9 +4652,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -4344,12 +4667,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J78" s="2" t="inlineStr">
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr">
+      <c r="L78" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4358,24 +4686,24 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>99050-7</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>165371010000101</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in bronchoalveolar lavage fluid at point in time by manual count (observable entity)</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Bronchoalveolar lavage by Manual count</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4386,9 +4714,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -4401,12 +4729,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J79" s="2" t="inlineStr">
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K79" s="2" t="inlineStr">
+      <c r="L79" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4415,24 +4748,24 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>26454-9</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>268871010000103</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in cerebrospinal fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Cerebral spinal fluid</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4443,9 +4776,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -4458,12 +4791,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J80" s="2" t="inlineStr">
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K80" s="2" t="inlineStr">
+      <c r="L80" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4472,24 +4810,24 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>791-4</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>260111010000100</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in cerebrospinal fluid at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Cerebral spinal fluid by Automated count</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4500,9 +4838,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -4515,12 +4853,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J81" s="2" t="inlineStr">
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K81" s="2" t="inlineStr">
+      <c r="L81" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4529,24 +4872,24 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>792-2</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>166351010000102</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in cerebrospinal fluid at point in time by manual count (observable entity)</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Cerebral spinal fluid by Manual count</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4557,9 +4900,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G82" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -4572,12 +4915,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J82" s="2" t="inlineStr">
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K82" s="2" t="inlineStr">
+      <c r="L82" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4586,24 +4934,24 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>76673-3</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>174301010000104</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in cerebrospinal fluid at point in time by manual count 1st tube (observable entity)</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Cerebral spinal fluid by Manual count --1st tube</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4614,9 +4962,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G83" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -4629,12 +4977,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J83" s="2" t="inlineStr">
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K83" s="2" t="inlineStr">
+      <c r="L83" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4643,24 +4996,24 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>46087-3</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>90911010000108</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in cerebrospinal fluid at point in time by manual count 2nd tube (observable entity)</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Cerebral spinal fluid by Manual count --2nd tube</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4671,9 +5024,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -4686,12 +5039,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J84" s="2" t="inlineStr">
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K84" s="2" t="inlineStr">
+      <c r="L84" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4700,24 +5058,24 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>46091-5</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>151291010000104</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in cerebrospinal fluid at point in time by manual count 3rd tube (observable entity)</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Cerebral spinal fluid by Manual count --3rd tube</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4728,9 +5086,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G85" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -4743,12 +5101,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J85" s="2" t="inlineStr">
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K85" s="2" t="inlineStr">
+      <c r="L85" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4757,24 +5120,24 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>46092-3</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>206801010000109</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in cerebrospinal fluid at point in time by manual count 4th tube (observable entity)</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Cerebral spinal fluid by Manual count --4th tube</t>
         </is>
       </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4785,9 +5148,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G86" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -4800,12 +5163,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J86" s="2" t="inlineStr">
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K86" s="2" t="inlineStr">
+      <c r="L86" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4814,24 +5182,24 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>47280-3</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>105281010000107</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in cord blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Cord blood</t>
         </is>
       </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4842,9 +5210,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G87" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -4857,12 +5225,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J87" s="2" t="inlineStr">
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K87" s="2" t="inlineStr">
+      <c r="L87" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4871,24 +5244,24 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>57841-9</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>63741010000103</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in dialysate at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Dialysis fluid by Automated count</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4899,9 +5272,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G88" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -4914,12 +5287,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J88" s="2" t="inlineStr">
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K88" s="2" t="inlineStr">
+      <c r="L88" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4928,24 +5306,24 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>53517-9</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>148681010000105</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in dialysate at point in time by manual count (observable entity)</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Dialysis fluid by Manual count</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4956,9 +5334,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G89" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -4971,12 +5349,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J89" s="2" t="inlineStr">
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K89" s="2" t="inlineStr">
+      <c r="L89" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4985,24 +5368,24 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>30387-5</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>122871010000106</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in gastric fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Gastric fluid</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5013,9 +5396,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G90" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -5028,12 +5411,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J90" s="2" t="inlineStr">
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K90" s="2" t="inlineStr">
+      <c r="L90" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5042,24 +5430,24 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>14372-7</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>189761010000107</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in gastric fluid at point in time by manual count (observable entity)</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Gastric fluid by Manual count</t>
         </is>
       </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5070,9 +5458,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G91" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -5085,12 +5473,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J91" s="2" t="inlineStr">
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K91" s="2" t="inlineStr">
+      <c r="L91" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5099,24 +5492,24 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>96727-3</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>182361010000103</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in lower respiratory tract at point in time by manual count (observable entity)</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Lower respiratory specimen by Manual count</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5127,9 +5520,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G92" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -5142,12 +5535,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J92" s="2" t="inlineStr">
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K92" s="2" t="inlineStr">
+      <c r="L92" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5156,24 +5554,24 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>30388-3</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>49061010000107</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in pericardial fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Pericardial fluid</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5184,9 +5582,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G93" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -5199,12 +5597,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J93" s="2" t="inlineStr">
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K93" s="2" t="inlineStr">
+      <c r="L93" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5213,24 +5616,24 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>57842-7</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>206081010000108</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in pericardial fluid at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Pericardial fluid by Automated count</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5241,9 +5644,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G94" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -5256,12 +5659,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J94" s="2" t="inlineStr">
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K94" s="2" t="inlineStr">
+      <c r="L94" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5270,24 +5678,24 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>14713-2</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>259061010000100</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in pericardial fluid at point in time by manual count (observable entity)</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Pericardial fluid by Manual count</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5298,9 +5706,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G95" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -5313,12 +5721,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J95" s="2" t="inlineStr">
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K95" s="2" t="inlineStr">
+      <c r="L95" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5327,24 +5740,24 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>81640-5</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>99551010000108</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in peritoneal dialysate at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Peritoneal dialysis fluid by Automated count</t>
         </is>
       </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5355,9 +5768,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G96" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -5370,12 +5783,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J96" s="2" t="inlineStr">
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K96" s="2" t="inlineStr">
+      <c r="L96" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5384,24 +5802,24 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>40534-0</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>79331010000101</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in peritoneal dialysate at point in time by manual count (observable entity)</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Peritoneal dialysis fluid by Manual count</t>
         </is>
       </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5412,9 +5830,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G97" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -5427,12 +5845,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J97" s="2" t="inlineStr">
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K97" s="2" t="inlineStr">
+      <c r="L97" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5441,24 +5864,24 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>26457-2</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>254911010000101</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in peritoneal fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Peritoneal fluid</t>
         </is>
       </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5469,9 +5892,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G98" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -5484,12 +5907,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J98" s="2" t="inlineStr">
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K98" s="2" t="inlineStr">
+      <c r="L98" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5498,24 +5926,24 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>57843-5</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>128641010000103</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in peritoneal fluid at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Peritoneal fluid by Automated count</t>
         </is>
       </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5526,9 +5954,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G99" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -5541,12 +5969,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr">
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K99" s="2" t="inlineStr">
+      <c r="L99" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5555,24 +5988,24 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>795-5</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>228571010000107</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in peritoneal fluid at point in time by manual count (observable entity)</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Peritoneal fluid by Manual count</t>
         </is>
       </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5583,9 +6016,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G100" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -5598,12 +6031,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J100" s="2" t="inlineStr">
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K100" s="2" t="inlineStr">
+      <c r="L100" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5612,24 +6050,24 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>26456-4</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>110421010000101</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in pleural fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Pleural fluid</t>
         </is>
       </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5640,9 +6078,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G101" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -5655,12 +6093,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J101" s="2" t="inlineStr">
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K101" s="2" t="inlineStr">
+      <c r="L101" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5669,24 +6112,24 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>794-8</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>176241010000104</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in pleural fluid at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Pleural fluid by Automated count</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5697,9 +6140,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G102" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -5712,12 +6155,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J102" s="2" t="inlineStr">
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K102" s="2" t="inlineStr">
+      <c r="L102" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5726,24 +6174,24 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>793-0</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>182781010000105</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in pleural fluid at point in time by manual count (observable entity)</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Pleural fluid by Manual count</t>
         </is>
       </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5754,9 +6202,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G103" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -5769,12 +6217,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J103" s="2" t="inlineStr">
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K103" s="2" t="inlineStr">
+      <c r="L103" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5783,24 +6236,24 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>67831-8</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>182601010000108</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in plr fld^Fetus at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Pleural fluid from Fetus</t>
         </is>
       </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5811,9 +6264,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G104" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -5826,12 +6279,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J104" s="2" t="inlineStr">
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K104" s="2" t="inlineStr">
+      <c r="L104" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5840,24 +6298,24 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>43245-0</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>274641010000107</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in seminal fluid at point in time by light microscopy (observable entity)</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Semen by Light microscopy</t>
         </is>
       </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5868,9 +6326,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G105" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -5883,12 +6341,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J105" s="2" t="inlineStr">
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K105" s="2" t="inlineStr">
+      <c r="L105" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5897,24 +6360,24 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>30389-1</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>85581010000101</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in seminal plasma at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Seminal plasma</t>
         </is>
       </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5925,9 +6388,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G106" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -5940,12 +6403,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J106" s="2" t="inlineStr">
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K106" s="2" t="inlineStr">
+      <c r="L106" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5954,24 +6422,24 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>16828-6</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>190201010000107</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in seminal plasma at point in time by manual count (observable entity)</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Seminal plasma by Manual count</t>
         </is>
       </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5982,9 +6450,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G107" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -5997,12 +6465,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J107" s="2" t="inlineStr">
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K107" s="2" t="inlineStr">
+      <c r="L107" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -6011,24 +6484,24 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>23859-2</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>146381010000104</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in specimen at point in time by light microscopy (observable entity)</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Specimen by Light microscopy</t>
         </is>
       </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6039,9 +6512,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G108" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -6054,12 +6527,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J108" s="2" t="inlineStr">
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K108" s="2" t="inlineStr">
+      <c r="L108" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -6068,24 +6546,24 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>26458-0</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>153771010000107</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in synovial fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Synovial fluid</t>
         </is>
       </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6096,9 +6574,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G109" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -6111,12 +6589,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J109" s="2" t="inlineStr">
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K109" s="2" t="inlineStr">
+      <c r="L109" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -6125,24 +6608,24 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>796-3</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>257201010000102</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in synovial fluid at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Synovial fluid by Automated count</t>
         </is>
       </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6153,9 +6636,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G110" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -6168,12 +6651,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J110" s="2" t="inlineStr">
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K110" s="2" t="inlineStr">
+      <c r="L110" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -6182,24 +6670,24 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>797-1</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>213761010000109</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in synovial fluid at point in time by manual count (observable entity)</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Synovial fluid by Manual count</t>
         </is>
       </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6210,9 +6698,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G111" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -6225,12 +6713,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J111" s="2" t="inlineStr">
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K111" s="2" t="inlineStr">
+      <c r="L111" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -6239,24 +6732,24 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30391-7</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>100381010000106</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in urine at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Urine</t>
         </is>
       </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6267,9 +6760,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G112" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -6282,12 +6775,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J112" s="2" t="inlineStr">
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K112" s="2" t="inlineStr">
+      <c r="L112" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -6296,24 +6794,24 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>798-9</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>231331010000107</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in urine at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Urine by Automated count</t>
         </is>
       </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6324,9 +6822,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G113" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -6339,12 +6837,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J113" s="2" t="inlineStr">
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K113" s="2" t="inlineStr">
+      <c r="L113" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -6353,24 +6856,24 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>799-7</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>269011010000106</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in urine at point in time by manual count (observable entity)</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Urine by Manual count</t>
         </is>
       </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6381,9 +6884,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G114" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
@@ -6396,12 +6899,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J114" s="2" t="inlineStr">
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K114" s="2" t="inlineStr">
+      <c r="L114" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -6410,24 +6918,24 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>105108-5</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>484391010000102</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in urine sediment at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Urine sediment</t>
         </is>
       </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6438,9 +6946,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G115" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -6453,12 +6961,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J115" s="2" t="inlineStr">
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K115" s="2" t="inlineStr">
+      <c r="L115" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -6467,24 +6980,24 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>5808-1</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>86471010000106</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in urine sediment at point in time by high power field light microscopy (observable entity)</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Urine sediment by Microscopy high power field</t>
         </is>
       </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6495,9 +7008,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G116" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -6510,12 +7023,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J116" s="2" t="inlineStr">
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K116" s="2" t="inlineStr">
+      <c r="L116" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -6524,24 +7042,24 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>68902-6</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>275451010000106</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in urine sediment by light microscopy (observable entity)</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] by Light microscopy in Urine sediment collected for unspecified duration</t>
         </is>
       </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6552,9 +7070,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G117" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
@@ -6567,12 +7085,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J117" s="2" t="inlineStr">
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K117" s="2" t="inlineStr">
+      <c r="L117" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -6581,24 +7104,24 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>68435-7</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>67351010000107</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in vitreous humor at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Vitreous fluid by Automated count</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6609,9 +7132,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G118" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
@@ -6624,12 +7147,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J118" s="2" t="inlineStr">
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K118" s="2" t="inlineStr">
+      <c r="L118" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -6638,27 +7166,27 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>57747-8</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>193321010000101</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in urine at point in time by automated test strip (observable entity)</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Urine by Automated test strip</t>
         </is>
       </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
@@ -6671,22 +7199,27 @@
           <t>·</t>
         </is>
       </c>
-      <c r="H119" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I119" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="J119" s="2" t="inlineStr">
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
         <is>
           <t>semiquantitative</t>
         </is>
       </c>
-      <c r="K119" s="2" t="inlineStr">
+      <c r="L119" s="2" t="inlineStr">
         <is>
           <t>Semi-quantitative scale (test strip)</t>
         </is>
@@ -6695,27 +7228,27 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>20409-9</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>239531010000102</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
         <is>
           <t>Number concentration of erythrocyte in urine at point in time by test strip (observable entity)</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Erythrocytes [#/volume] in Urine by Test strip</t>
         </is>
       </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
@@ -6728,29 +7261,34 @@
           <t>·</t>
         </is>
       </c>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I120" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="J120" s="2" t="inlineStr">
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I120" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
         <is>
           <t>semiquantitative</t>
         </is>
       </c>
-      <c r="K120" s="2" t="inlineStr">
+      <c r="L120" s="2" t="inlineStr">
         <is>
           <t>Semi-quantitative scale (test strip)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A12:K120"/>
+  <autoFilter ref="A12:L120"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>